--- a/artfynd/A 36596-2023 artfynd.xlsx
+++ b/artfynd/A 36596-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36596-2023 artfynd.xlsx
+++ b/artfynd/A 36596-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110232841</v>
+        <v>56754963</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,57 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borås, Vg</t>
+          <t>Klinten,  väg O1773, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374073.4231623174</v>
+        <v>374074</v>
       </c>
       <c r="R2" t="n">
-        <v>6412438.000376272</v>
+        <v>6412421</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2013-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,16 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Gudmundson</t>
+          <t>John Rolander Borlid</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Gudmundson</t>
+          <t>Tove Adelsköld, Åsa Röstell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -811,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110232856</v>
+        <v>79204472</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,36 +809,24 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borås, Vg</t>
+          <t>Klinten, klinten, väg 1773, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374052.476113938</v>
+        <v>374043</v>
       </c>
       <c r="R3" t="n">
-        <v>6412433.86229576</v>
+        <v>6412430</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,21 +864,507 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Anna Dahlén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110232841</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borås, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>374073</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6412438</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Amanda Gudmundson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Amanda Gudmundson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110232856</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Borås, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>374052</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6412434</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>82945244</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klinten, klinten, väg 1773, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>374079</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6412425</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Dahlén, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82945249</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klinten, klinten, väg 1773, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>374182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6412437</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Naalisvaara Engman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Dahlén, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 36596-2023 artfynd.xlsx
+++ b/artfynd/A 36596-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56754963</t>
         </is>
       </c>
     </row>
@@ -889,6 +899,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79204472</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82945244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82945249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110232841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,8 +1399,21 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110232856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>